--- a/docs/superpowers/plans/restructure-and-test-rewrite/sonnet-session-plan.xlsx
+++ b/docs/superpowers/plans/restructure-and-test-rewrite/sonnet-session-plan.xlsx
@@ -1703,7 +1703,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ASKIDA</t>
+          <t>TAMAMLANDI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASKIDA</t>
+          <t>TAMAMLANDI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1820,6 +1820,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -1864,6 +1865,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -1931,6 +1933,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
